--- a/prospect-list-hospitality.xlsx
+++ b/prospect-list-hospitality.xlsx
@@ -1469,27 +1469,27 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Justin McMillen</t>
+          <t>Clare Wallace Voss</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Culinary Director</t>
+          <t>Director of Communication</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Mid-size chef-led group - one yes closes it</t>
+          <t>Comms/brand owner; small group (~46 staff) so short path to Gerard Craft. Backup: Peter Slay, Dir of Culinary Operations</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>find domain + verify first</t>
+          <t>cvoss@nichestlouis.com or clare@nichestlouis.com (verify; domain confirmed from site). Old @nichegroup.com is DEAD - McMillen mailbox invalid</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>WAVE 2</t>
+          <t>WAVE 2 | Pastaria demo file ready (catches: castlevetrano, alrdo, no allergens)</t>
         </is>
       </c>
     </row>
